--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4967-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4967-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC406FB-E85A-474C-A0DF-A2B5562CA165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{103FF177-D58A-49E4-8AA6-26F06489B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DC254FB9-A748-4591-865D-5B877CC5B6C7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{099614B5-1B93-448B-8D85-68B8117106AE}"/>
   </bookViews>
   <sheets>
     <sheet name="4967-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,23 +1400,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E43AF2D-8CE5-4CC1-B266-B52EDFB43957}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A819B0-C7C4-4A6C-AE69-2F2434B0D48E}">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="12" width="7.77734375" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="7.88671875" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1570,7 +1570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2026</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2025</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2024</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2023</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2022</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2021</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2020</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2018</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2017</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2016</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2015</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2014</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2013</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2012</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2011</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>2010</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
         <v>25</v>
       </c>
